--- a/Lưu lượng Sản lượng Buôn Tua Srah 1977_2026.xlsx
+++ b/Lưu lượng Sản lượng Buôn Tua Srah 1977_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VScode\Du lieu truy van chuoi dong dang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F998DDF-D102-4CA1-995D-BC47C9FED6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B942B3-8B31-43F3-A694-BE70C5222EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1575" windowWidth="29040" windowHeight="15960" xr2:uid="{C165E8D0-C032-438C-AC6C-C00CEECF28F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{C165E8D0-C032-438C-AC6C-C00CEECF28F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BTS" sheetId="2" r:id="rId1"/>
@@ -1216,14 +1216,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5965C0F6-95C9-4EEE-8278-0B2FB411F07A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{5965C0F6-95C9-4EEE-8278-0B2FB411F07A}">
   <dimension ref="A1:AF81"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" ns3:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="15" ns3:dyDescent="0.25">
       <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
       <c r="AA1" s="24"/>
       <c r="AB1" s="24"/>
     </row>
-    <row r="2" spans="1:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="15" ns3:dyDescent="0.25">
       <c r="C2" s="1">
         <v>1</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" ns3:dyDescent="0.2">
       <c r="B3">
         <v>1977</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" ns3:dyDescent="0.2">
       <c r="B4">
         <v>1978</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" ns3:dyDescent="0.2">
       <c r="B5">
         <v>1979</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>81.2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" ns3:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6">
         <v>1980</v>
@@ -1722,7 +1722,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" ns3:dyDescent="0.2">
       <c r="B7">
         <v>1981</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" ns3:dyDescent="0.2">
       <c r="B8">
         <v>1982</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" ns3:dyDescent="0.2">
       <c r="B9">
         <v>1983</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" ns3:dyDescent="0.2">
       <c r="B10">
         <v>1984</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" ns3:dyDescent="0.2">
       <c r="B11">
         <v>1985</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" ns3:dyDescent="0.2">
       <c r="B12">
         <v>1986</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" ns3:dyDescent="0.2">
       <c r="B13">
         <v>1987</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" ns3:dyDescent="0.2">
       <c r="B14">
         <v>1988</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>81.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" ns3:dyDescent="0.2">
       <c r="B15">
         <v>1989</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>56.3</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" ns3:dyDescent="0.2">
       <c r="B16">
         <v>1990</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:28" ns3:dyDescent="0.2">
       <c r="B17">
         <v>1991</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:28" ns3:dyDescent="0.2">
       <c r="B18">
         <v>1992</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>92.7</v>
       </c>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:28" ns3:dyDescent="0.2">
       <c r="B19">
         <v>1993</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:28" ns3:dyDescent="0.2">
       <c r="B20">
         <v>1994</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:28" ns3:dyDescent="0.2">
       <c r="B21">
         <v>1995</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>64.7</v>
       </c>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:28" ns3:dyDescent="0.2">
       <c r="B22">
         <v>1996</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:28" ns3:dyDescent="0.2">
       <c r="B23">
         <v>1997</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:28" ns3:dyDescent="0.2">
       <c r="B24">
         <v>1998</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:28" ns3:dyDescent="0.2">
       <c r="B25">
         <v>1999</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:28" ns3:dyDescent="0.2">
       <c r="B26">
         <v>2000</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:28" ns3:dyDescent="0.2">
       <c r="B27">
         <v>2001</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:28" ns3:dyDescent="0.2">
       <c r="B28">
         <v>2002</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:28" ns3:dyDescent="0.2">
       <c r="B29">
         <v>2003</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:28" ns3:dyDescent="0.2">
       <c r="B30">
         <v>2004</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:28" ns3:dyDescent="0.2">
       <c r="B31">
         <v>2005</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:28" ns3:dyDescent="0.2">
       <c r="B32">
         <v>2006</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" ns3:dyDescent="0.2">
       <c r="B33">
         <v>2007</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>95.2</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" ns3:dyDescent="0.2">
       <c r="B34">
         <v>2008</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>79.3</v>
       </c>
     </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:28" ns3:dyDescent="0.2">
       <c r="B35">
         <v>2009</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>79.3</v>
       </c>
     </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:28" ns3:dyDescent="0.2">
       <c r="B36">
         <v>2010</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>87.431612903225798</v>
       </c>
     </row>
-    <row r="37" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B37" s="9">
         <v>2011</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>78.933500597372273</v>
       </c>
     </row>
-    <row r="38" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B38" s="12">
         <v>2012</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>50.229206989236509</v>
       </c>
     </row>
-    <row r="39" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B39" s="12">
         <v>2013</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>56.430753882905776</v>
       </c>
     </row>
-    <row r="40" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B40" s="12">
         <v>2014</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>56.586698924764292</v>
       </c>
     </row>
-    <row r="41" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B41" s="12">
         <v>2015</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>49.560215247355998</v>
       </c>
     </row>
-    <row r="42" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B42" s="12">
         <v>2016</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>135.96849792845055</v>
       </c>
     </row>
-    <row r="43" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B43" s="12">
         <v>2017</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>118.3095881519756</v>
       </c>
     </row>
-    <row r="44" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B44" s="12">
         <v>2018</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>84.968060161558284</v>
       </c>
     </row>
-    <row r="45" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B45" s="12">
         <v>2019</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>66.735622909200004</v>
       </c>
     </row>
-    <row r="46" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B46" s="12">
         <v>2020</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>120.95</v>
       </c>
     </row>
-    <row r="47" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B47" s="12">
         <v>2021</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>132.20188172043012</v>
       </c>
     </row>
-    <row r="48" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B48" s="12">
         <v>2022</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>76.388763440860231</v>
       </c>
     </row>
-    <row r="49" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B49" s="12">
         <v>2023</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B50" s="14">
         <v>2024</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>112.0967806451613</v>
       </c>
     </row>
-    <row r="51" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B51" s="17">
         <v>2025</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>148.00941290322578</v>
       </c>
     </row>
-    <row r="52" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B52" s="17">
         <v>2026</v>
       </c>
@@ -5928,7 +5928,9 @@
       <c r="K52" s="8">
         <v>37.911999999999999</v>
       </c>
-      <c r="L52" s="8"/>
+      <c r="L52" s="8" t="n">
+        <v>15.9484973</v>
+      </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
       <c r="O52" s="18"/>
@@ -5960,8 +5962,11 @@
       <c r="Y52" s="8">
         <v>250.98</v>
       </c>
-    </row>
-    <row r="53" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+      <c r="Z52" s="8" t="n">
+        <v>205.92</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B53" s="17"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -5978,7 +5983,7 @@
       <c r="O53" s="18"/>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B54" s="17"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -5995,7 +6000,7 @@
       <c r="O54" s="18"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B55" s="19"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
@@ -6012,7 +6017,7 @@
       <c r="O55" s="21"/>
       <c r="P55" s="4"/>
     </row>
-    <row r="56" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B56" s="19"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
@@ -6029,7 +6034,7 @@
       <c r="O56" s="21"/>
       <c r="P56" s="4"/>
     </row>
-    <row r="57" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B57" s="19"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -6046,7 +6051,7 @@
       <c r="O57" s="21"/>
       <c r="P57" s="4"/>
     </row>
-    <row r="58" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B58" s="26"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
@@ -6063,7 +6068,7 @@
       <c r="O58" s="21"/>
       <c r="P58" s="4"/>
     </row>
-    <row r="59" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B59" s="26"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -6080,7 +6085,7 @@
       <c r="O59" s="21"/>
       <c r="P59" s="4"/>
     </row>
-    <row r="60" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B60" s="19"/>
       <c r="C60" s="22"/>
       <c r="D60" s="22"/>
@@ -6097,7 +6102,7 @@
       <c r="O60" s="21"/>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B61" s="19"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -6114,7 +6119,7 @@
       <c r="O61" s="21"/>
       <c r="P61" s="4"/>
     </row>
-    <row r="62" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B62" s="19"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
@@ -6131,7 +6136,7 @@
       <c r="O62" s="23"/>
       <c r="P62" s="4"/>
     </row>
-    <row r="63" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B63" s="19"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
@@ -6148,7 +6153,7 @@
       <c r="O63" s="23"/>
       <c r="P63" s="4"/>
     </row>
-    <row r="64" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B64" s="19"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -6165,7 +6170,7 @@
       <c r="O64" s="23"/>
       <c r="P64" s="4"/>
     </row>
-    <row r="65" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B65" s="19"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
@@ -6182,7 +6187,7 @@
       <c r="O65" s="23"/>
       <c r="P65" s="4"/>
     </row>
-    <row r="66" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B66" s="19"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -6199,7 +6204,7 @@
       <c r="O66" s="23"/>
       <c r="P66" s="4"/>
     </row>
-    <row r="67" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B67" s="19"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -6216,7 +6221,7 @@
       <c r="O67" s="23"/>
       <c r="P67" s="4"/>
     </row>
-    <row r="68" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B68" s="19"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -6233,7 +6238,7 @@
       <c r="O68" s="23"/>
       <c r="P68" s="4"/>
     </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:28" ns3:dyDescent="0.2">
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
@@ -6247,7 +6252,7 @@
       <c r="M71" s="8"/>
       <c r="N71" s="8"/>
     </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:28" ns3:dyDescent="0.2">
       <c r="C74" s="27"/>
       <c r="D74" s="27"/>
       <c r="E74" s="27"/>
@@ -6263,7 +6268,7 @@
       <c r="V74" s="27"/>
       <c r="W74" s="27"/>
     </row>
-    <row r="75" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6290,7 +6295,7 @@
       <c r="AA75" s="3"/>
       <c r="AB75" s="3"/>
     </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:28" ns3:dyDescent="0.2">
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -6305,7 +6310,7 @@
       <c r="N76" s="5"/>
       <c r="O76" s="6"/>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" ns3:dyDescent="0.2">
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
